--- a/data/trans_bre/IP2002-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP2002-Estudios-trans_bre.xlsx
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,49; 4,58</t>
+          <t>-8,61; 4,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,52; 8,97</t>
+          <t>-7,18; 8,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 9,9</t>
+          <t>-2,71; 9,96</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 5,37</t>
+          <t>-3,99; 4,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-68,8; 90,18</t>
+          <t>-68,33; 86,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-50,7; 155,92</t>
+          <t>-49,25; 155,02</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-77,54; 1210,72</t>
+          <t>-78,5; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 3,02</t>
+          <t>-3,17; 2,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 0,47</t>
+          <t>-4,51; 0,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 4,44</t>
+          <t>-0,79; 4,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 3,75</t>
+          <t>-1,34; 3,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-29,22; 48,62</t>
+          <t>-35,24; 46,43</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-54,86; 9,66</t>
+          <t>-53,81; 12,86</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-15,16; 111,82</t>
+          <t>-12,71; 115,44</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-26,44; 117,5</t>
+          <t>-27,23; 121,55</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 4,49</t>
+          <t>-4,51; 4,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 2,39</t>
+          <t>-5,28; 2,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 3,58</t>
+          <t>-4,28; 3,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 6,26</t>
+          <t>-4,6; 6,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-55,11; 138,42</t>
+          <t>-55,19; 121,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-75,08; 101,05</t>
+          <t>-72,63; 91,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-65,09; 143,44</t>
+          <t>-62,89; 129,09</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-40,71; 113,74</t>
+          <t>-43,92; 117,49</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 2,1</t>
+          <t>-2,49; 2,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 0,83</t>
+          <t>-3,76; 0,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 3,61</t>
+          <t>-0,6; 3,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 2,89</t>
+          <t>-1,15; 3,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-31,1; 33,3</t>
+          <t>-31,46; 34,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-45,59; 15,27</t>
+          <t>-46,31; 13,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-12,57; 94,65</t>
+          <t>-10,23; 87,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-24,51; 69,0</t>
+          <t>-19,07; 89,33</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2002-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP2002-Estudios-trans_bre.xlsx
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,61; 4,57</t>
+          <t>-8,6; 4,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,18; 8,88</t>
+          <t>-7,58; 8,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 9,96</t>
+          <t>-1,93; 9,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 4,96</t>
+          <t>-4,05; 5,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-68,33; 86,41</t>
+          <t>-68,58; 80,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-49,25; 155,02</t>
+          <t>-50,31; 137,87</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-78,5; —</t>
+          <t>-69,53; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 2,81</t>
+          <t>-3,01; 2,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 0,61</t>
+          <t>-4,55; 0,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 4,48</t>
+          <t>-0,89; 4,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 3,92</t>
+          <t>-1,39; 3,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-35,24; 46,43</t>
+          <t>-34,72; 44,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-53,81; 12,86</t>
+          <t>-53,96; 20,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-12,71; 115,44</t>
+          <t>-15,09; 114,86</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-27,23; 121,55</t>
+          <t>-26,62; 128,12</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 4,44</t>
+          <t>-4,01; 4,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 2,34</t>
+          <t>-5,2; 2,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 3,52</t>
+          <t>-3,85; 3,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 6,12</t>
+          <t>-4,84; 6,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-55,19; 121,23</t>
+          <t>-53,32; 131,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-72,63; 91,26</t>
+          <t>-73,97; 102,72</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-62,89; 129,09</t>
+          <t>-63,51; 135,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-43,92; 117,49</t>
+          <t>-44,3; 116,22</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 2,06</t>
+          <t>-2,46; 2,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 0,76</t>
+          <t>-3,75; 0,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 3,49</t>
+          <t>-0,75; 3,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 3,26</t>
+          <t>-1,22; 3,23</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-31,46; 34,22</t>
+          <t>-29,5; 35,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-46,31; 13,9</t>
+          <t>-45,08; 11,36</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-10,23; 87,79</t>
+          <t>-14,0; 85,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-19,07; 89,33</t>
+          <t>-21,37; 81,55</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2002-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP2002-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,45</t>
+          <t>0,73</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>34,94%</t>
         </is>
       </c>
     </row>
@@ -660,37 +660,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,6; 4,19</t>
+          <t>-8,49; 4,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,58; 8,29</t>
+          <t>-7,52; 8,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 9,76</t>
+          <t>-2,63; 9,9</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 5,11</t>
+          <t>-4,69; 5,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-68,58; 80,98</t>
+          <t>-68,8; 90,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-50,31; 137,87</t>
+          <t>-50,7; 155,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-69,53; —</t>
+          <t>-77,54; 1210,72</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,1</t>
+          <t>1,22</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>28,66%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 2,74</t>
+          <t>-2,5; 3,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 0,97</t>
+          <t>-4,55; 0,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 4,55</t>
+          <t>-0,89; 4,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 3,86</t>
+          <t>-1,06; 3,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-34,72; 44,93</t>
+          <t>-29,22; 48,62</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-53,96; 20,78</t>
+          <t>-54,86; 9,66</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-15,09; 114,86</t>
+          <t>-15,16; 111,82</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-26,62; 128,12</t>
+          <t>-23,76; 115,98</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,86</t>
+          <t>1,27</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>16,06%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 4,5</t>
+          <t>-4,42; 4,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,2; 2,81</t>
+          <t>-5,24; 2,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 3,6</t>
+          <t>-4,06; 3,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 6,31</t>
+          <t>-3,94; 6,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-53,32; 131,15</t>
+          <t>-55,11; 138,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-73,97; 102,72</t>
+          <t>-75,08; 101,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-63,51; 135,4</t>
+          <t>-65,09; 143,44</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-44,3; 116,22</t>
+          <t>-35,62; 125,71</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,92</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>24,02%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 2,15</t>
+          <t>-2,61; 2,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 0,64</t>
+          <t>-3,64; 0,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 3,43</t>
+          <t>-0,67; 3,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 3,23</t>
+          <t>-1,09; 3,33</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-29,5; 35,04</t>
+          <t>-31,1; 33,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-45,08; 11,36</t>
+          <t>-45,59; 15,27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-14,0; 85,88</t>
+          <t>-12,57; 94,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-21,37; 81,55</t>
+          <t>-18,91; 82,83</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP2002-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP2002-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,195 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-1,83</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,55</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3,1</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,73</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-20,12%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>5,27%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>105,74%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>34,94%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-1.825911835845399</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.5512605092592757</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>3.099264589667547</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0.728378748850294</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.201245832018353</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.05272251103876486</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>1.057365339158807</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0.3493546338899408</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-8,49; 4,58</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-7,52; 8,97</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-2,63; 9,9</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-4,69; 5,79</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-68,8; 90,18</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-50,7; 155,92</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-77,54; 1210,72</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-8.487759157335832</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-7.523835627875755</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-2.629550917566799</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-4.686365418142115</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.6880347497597323</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.5070233375268923</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.7754159098318057</v>
+      </c>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>4.575591600873862</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>8.97310174007499</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>9.90093197262407</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>5.793246214578883</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.9017576064432379</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>1.559174223948011</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>12.10724983236733</v>
+      </c>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,07</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-1,91</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1,79</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1,22</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-27,45%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>34,7%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>28,66%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-2,5; 3,02</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-4,55; 0,47</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-0,89; 4,44</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-1,06; 3,76</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-29,22; 48,62</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-54,86; 9,66</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-15,16; 111,82</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-23,76; 115,98</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>0.06631652110350578</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-1.911911441213414</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1.790637476713408</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>1.22083825768864</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.008887352605934488</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.2745027908818607</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.3469994286018151</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0.286648242683664</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0,25</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-1,29</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,32</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,27</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>4,28%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-25,82%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-6,95%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>16,06%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-2.504345492863044</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-4.552131051293386</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-0.8945192902073175</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-1.059827035020214</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.2921717528254192</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.5486430733184919</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.1515892887112855</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.2376146759585493</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-4,42; 4,49</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-5,24; 2,39</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-4,06; 3,58</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-3,94; 6,67</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-55,11; 138,42</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-75,08; 101,05</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-65,09; 143,44</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-35,62; 125,71</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>3.019660964009453</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.469957828895181</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>4.43579517015768</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>3.755642249813863</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.486204573792543</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.09657163079211195</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>1.118160673643432</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>1.159778866602692</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,97 +815,197 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-0,19</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-1,4</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1,4</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1,2</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-2,54%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-20,22%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>29,16%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>24,02%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>0.2463170430854998</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-1.28570829779343</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.3195238485022178</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>1.272328517823953</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.04284438637899578</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.2582368450815299</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.06945542231080222</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.160554704279379</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-2,61; 2,1</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-3,64; 0,83</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-0,67; 3,61</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-1,09; 3,33</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-31,1; 33,3</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-45,59; 15,27</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-12,57; 94,65</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-18,91; 82,83</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-4.423533683891919</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-5.237333268680889</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-4.058121704375314</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-3.940182950284622</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.5510664110522003</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.7508305693574954</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.6508653341599989</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.3562189595358535</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>4.488306186802242</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>2.39186564597747</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>3.582835339242324</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>6.665984832527013</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>1.38422150101538</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>1.010499183124774</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>1.43443522558246</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>1.257128749074907</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-0.1854564434951272</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-1.402313782370399</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>1.402504110776862</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>1.195112280791465</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.02544311645924876</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.2022246476191238</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.2915529311512513</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>0.2401730366816887</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-2.614819397149473</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-3.644225151151304</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-0.6731146281087408</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-1.087335743602655</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.3109664710022951</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.4559406269527628</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.125654092743635</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.1891314996998807</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>2.100615929546119</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.8267476289092088</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>3.61371364061364</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>3.328674250496395</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.3330459699326585</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.1526818681770171</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.9465367714625371</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.8282765804420478</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1008,13 +1013,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
